--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_arica_y_parinacota.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>35.1057801284473</v>
+      </c>
+      <c r="C2">
         <v>24.90420422041125</v>
-      </c>
-      <c r="C2">
-        <v>35.1057801284473</v>
       </c>
       <c r="D2">
         <v>4.015386282370788</v>
       </c>
       <c r="E2">
-        <v>15.56415640046208</v>
+        <v>21.93974349244897</v>
       </c>
       <c r="F2">
         <v>62.49610010708895</v>
       </c>
       <c r="G2">
-        <v>21.93974349244897</v>
+        <v>15.56415640046208</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>41.43646408839779</v>
+      </c>
+      <c r="C3">
         <v>58.28729281767956</v>
-      </c>
-      <c r="C3">
-        <v>41.43646408839779</v>
       </c>
       <c r="D3">
         <v>1.71563981042654</v>
       </c>
       <c r="E3">
-        <v>29.18395573997234</v>
+        <v>20.74688796680498</v>
       </c>
       <c r="F3">
         <v>50.06915629322268</v>
       </c>
       <c r="G3">
-        <v>20.74688796680498</v>
+        <v>29.18395573997233</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>40.77809798270894</v>
+      </c>
+      <c r="C4">
         <v>42.07492795389049</v>
-      </c>
-      <c r="C4">
-        <v>40.77809798270894</v>
       </c>
       <c r="D4">
         <v>2.376712328767123</v>
       </c>
       <c r="E4">
-        <v>23.01024428684003</v>
+        <v>22.301024428684</v>
       </c>
       <c r="F4">
         <v>54.68873128447596</v>
       </c>
       <c r="G4">
-        <v>22.301024428684</v>
+        <v>23.01024428684003</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>44.64285714285715</v>
+      </c>
+      <c r="C5">
         <v>35.26785714285715</v>
-      </c>
-      <c r="C5">
-        <v>44.64285714285715</v>
       </c>
       <c r="D5">
         <v>2.835443037974684</v>
       </c>
       <c r="E5">
-        <v>19.6029776674938</v>
+        <v>24.81389578163772</v>
       </c>
       <c r="F5">
         <v>55.58312655086849</v>
       </c>
       <c r="G5">
-        <v>24.81389578163772</v>
+        <v>19.6029776674938</v>
       </c>
     </row>
   </sheetData>
